--- a/KatalonData/RADTestData/BeforePayments.xlsx
+++ b/KatalonData/RADTestData/BeforePayments.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
@@ -27,7 +27,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="527">
   <si>
     <t>Result</t>
   </si>
@@ -730,12 +730,910 @@
   </si>
   <si>
     <t>Sun Aug 02 21:23:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:17:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:18:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:19:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:20:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:21:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:22:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:23:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:24:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:25:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:26:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:27:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:28:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:30:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:31:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:33:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:34:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:35:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:36:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:37:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:38:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:39:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:41:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:42:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:43:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:44:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:45:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:47:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:48:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:49:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:50:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:51:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:52:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:53:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:54:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:55:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:56:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:57:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:58:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:59:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:00:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:01:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:02:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:03:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:04:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:05:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:06:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:07:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:08:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:09:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:10:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:11:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:12:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:13:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:14:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:15:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:16:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:18:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:19:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:20:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:21:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:22:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:23:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:24:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:25:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:26:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:27:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:28:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:29:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:30:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:31:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:31:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:33:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:33:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:34:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:35:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:36:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:37:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:38:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:39:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:40:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:41:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:42:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:43:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:44:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:45:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:46:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:47:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:48:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:49:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:50:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:51:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:52:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:53:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:54:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:56:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:57:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:58:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 04:59:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:00:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:01:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:02:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:03:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:04:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:05:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:06:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:07:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:08:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:09:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:10:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:11:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:13:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:13:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:14:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:15:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:16:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:17:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:18:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:19:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:20:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:21:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:22:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:23:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:24:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:25:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:26:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:27:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:28:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:29:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:30:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:31:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:32:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:33:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:34:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:35:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:36:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:37:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:38:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:39:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:40:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:41:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:42:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:43:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:44:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:44:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:46:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:47:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:48:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:49:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:50:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:51:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:52:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:53:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:55:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:56:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:58:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 05:59:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:01:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:02:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:03:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:04:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:05:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:06:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:07:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:08:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:08:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:09:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:10:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:11:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:12:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:14:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:14:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:15:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:16:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:17:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:18:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:19:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:20:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:21:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:23:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:24:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:25:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:26:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:27:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:28:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:29:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:29:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:30:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:31:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:32:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:33:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:34:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:35:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:36:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:37:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:38:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:39:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:40:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:41:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:42:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:43:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:44:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:45:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:46:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:47:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:48:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:49:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:49:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:50:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:51:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:52:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:53:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:54:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:56:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:56:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:57:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:58:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 06:59:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:01:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:02:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:03:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:04:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:05:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:06:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:07:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:08:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:08:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:09:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:10:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:11:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:12:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:13:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:14:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:15:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:16:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:17:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:18:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:19:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:20:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:21:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:22:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:23:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:24:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:25:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:26:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:27:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:28:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:29:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:30:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:31:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:32:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:33:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:34:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:35:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:36:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:37:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:38:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:39:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:40:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:41:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:42:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:43:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:44:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:45:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:46:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:47:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:47:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:49:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:50:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:50:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:51:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:53:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:54:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:55:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:56:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:58:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 07:59:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 08:00:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 08:01:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 08:02:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 08:03:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 08:04:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 08:05:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 08:06:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 08:07:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 08:08:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 08:09:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 08:10:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 08:11:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 08:12:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 08:13:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 08:14:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 08:16:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 08:18:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 08:20:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 08:21:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 08:23:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 08:25:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 08:27:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 21:48:48 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1108,17 +2006,17 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="14.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="18.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="18.46484375" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1158,7 +2056,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>122</v>
+        <v>228</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1187,7 +2085,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>123</v>
+        <v>229</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1216,7 +2114,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>124</v>
+        <v>230</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1248,7 +2146,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>125</v>
+        <v>231</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1280,7 +2178,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>126</v>
+        <v>232</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1312,7 +2210,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>127</v>
+        <v>233</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1344,7 +2242,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>128</v>
+        <v>234</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1377,16 +2275,16 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="52" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="43.33203125" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.59765625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="52.0" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="43.33203125" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1426,7 +2324,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>129</v>
+        <v>235</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1449,7 +2347,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>130</v>
+        <v>236</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1472,7 +2370,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>131</v>
+        <v>237</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1495,7 +2393,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>132</v>
+        <v>238</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1521,7 +2419,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>133</v>
+        <v>239</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1547,7 +2445,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>134</v>
+        <v>240</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1570,7 +2468,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>135</v>
+        <v>241</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1593,7 +2491,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>136</v>
+        <v>242</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -1616,7 +2514,7 @@
         <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>137</v>
+        <v>243</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -1639,7 +2537,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>138</v>
+        <v>244</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -1662,7 +2560,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>139</v>
+        <v>245</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -1685,7 +2583,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>140</v>
+        <v>246</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -1708,7 +2606,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>141</v>
+        <v>247</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -1731,7 +2629,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>142</v>
+        <v>248</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -1751,7 +2649,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>143</v>
+        <v>249</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -1777,7 +2675,7 @@
         <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>144</v>
+        <v>250</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -1800,7 +2698,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>145</v>
+        <v>251</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -1840,7 +2738,7 @@
         <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>146</v>
+        <v>252</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -1885,15 +2783,15 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -1930,7 +2828,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>147</v>
+        <v>253</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1956,7 +2854,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>148</v>
+        <v>254</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1979,7 +2877,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>149</v>
+        <v>255</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -2005,7 +2903,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>150</v>
+        <v>256</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2031,7 +2929,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>151</v>
+        <v>257</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -2057,7 +2955,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>152</v>
+        <v>258</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2092,17 +2990,17 @@
   <dimension ref="A1:M64"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="41.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="10" width="19.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="19.796875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.19921875" style="1" collapsed="1"/>
-    <col min="13" max="13" width="43.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="41.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="10" customWidth="true" style="1" width="19.796875" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="1" width="19.796875"/>
+    <col min="12" max="12" style="1" width="9.19921875" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="43.19921875" collapsed="true"/>
+    <col min="14" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
@@ -2151,7 +3049,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>153</v>
+        <v>439</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -2174,7 +3072,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>154</v>
+        <v>440</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -2200,7 +3098,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>155</v>
+        <v>441</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -2226,7 +3124,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>156</v>
+        <v>442</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2252,7 +3150,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>157</v>
+        <v>443</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -2278,7 +3176,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>158</v>
+        <v>444</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2301,7 +3199,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>159</v>
+        <v>445</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -2327,7 +3225,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>160</v>
+        <v>446</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -2353,7 +3251,7 @@
         <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>161</v>
+        <v>447</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -2379,7 +3277,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>162</v>
+        <v>448</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -2405,7 +3303,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>163</v>
+        <v>449</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -2428,7 +3326,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>164</v>
+        <v>450</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -2454,7 +3352,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>165</v>
+        <v>451</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -2480,7 +3378,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>166</v>
+        <v>452</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -2506,7 +3404,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>167</v>
+        <v>453</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -2532,7 +3430,7 @@
         <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>168</v>
+        <v>454</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -2561,7 +3459,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>169</v>
+        <v>455</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -2590,7 +3488,7 @@
         <v>35</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>170</v>
+        <v>456</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>32</v>
@@ -2619,7 +3517,7 @@
         <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>171</v>
+        <v>457</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -2642,7 +3540,7 @@
         <v>35</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>172</v>
+        <v>458</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>32</v>
@@ -2671,7 +3569,7 @@
         <v>35</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>173</v>
+        <v>459</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>32</v>
@@ -2700,7 +3598,7 @@
         <v>35</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>174</v>
+        <v>460</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>32</v>
@@ -2726,7 +3624,7 @@
         <v>35</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>175</v>
+        <v>461</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>32</v>
@@ -2755,7 +3653,7 @@
         <v>35</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>176</v>
+        <v>462</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>32</v>
@@ -2787,7 +3685,7 @@
         <v>35</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>177</v>
+        <v>463</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>32</v>
@@ -2816,7 +3714,7 @@
         <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>178</v>
+        <v>464</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>32</v>
@@ -2845,7 +3743,7 @@
         <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>179</v>
+        <v>465</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>32</v>
@@ -2877,7 +3775,7 @@
         <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>180</v>
+        <v>466</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>32</v>
@@ -2906,7 +3804,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>181</v>
+        <v>526</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>32</v>
@@ -2935,7 +3833,7 @@
         <v>35</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>182</v>
+        <v>468</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>32</v>
@@ -2964,7 +3862,7 @@
         <v>35</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>183</v>
+        <v>469</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>32</v>
@@ -2987,7 +3885,7 @@
         <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>184</v>
+        <v>470</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>32</v>
@@ -3016,7 +3914,7 @@
         <v>35</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>185</v>
+        <v>471</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>32</v>
@@ -3045,7 +3943,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>186</v>
+        <v>472</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>32</v>
@@ -3071,7 +3969,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>187</v>
+        <v>473</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>32</v>
@@ -3100,7 +3998,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>188</v>
+        <v>474</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>32</v>
@@ -3132,7 +4030,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>189</v>
+        <v>475</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>32</v>
@@ -3161,7 +4059,7 @@
         <v>35</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>190</v>
+        <v>476</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>32</v>
@@ -3190,7 +4088,7 @@
         <v>35</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>191</v>
+        <v>477</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>32</v>
@@ -3222,7 +4120,7 @@
         <v>35</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>192</v>
+        <v>478</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>32</v>
@@ -3251,7 +4149,7 @@
         <v>35</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>193</v>
+        <v>479</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>32</v>
@@ -3280,7 +4178,7 @@
         <v>35</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>194</v>
+        <v>480</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>32</v>
@@ -3309,7 +4207,7 @@
         <v>35</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>195</v>
+        <v>481</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>32</v>
@@ -3332,7 +4230,7 @@
         <v>35</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>196</v>
+        <v>482</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>32</v>
@@ -3361,7 +4259,7 @@
         <v>35</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>197</v>
+        <v>483</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>32</v>
@@ -3390,7 +4288,7 @@
         <v>35</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>198</v>
+        <v>484</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>32</v>
@@ -3416,7 +4314,7 @@
         <v>35</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>199</v>
+        <v>485</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>32</v>
@@ -3445,7 +4343,7 @@
         <v>35</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>200</v>
+        <v>486</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>32</v>
@@ -3477,7 +4375,7 @@
         <v>35</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>201</v>
+        <v>487</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>32</v>
@@ -3506,7 +4404,7 @@
         <v>35</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>202</v>
+        <v>488</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>32</v>
@@ -3535,7 +4433,7 @@
         <v>35</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>203</v>
+        <v>489</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>32</v>
@@ -3567,7 +4465,7 @@
         <v>35</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>204</v>
+        <v>490</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>32</v>
@@ -3587,10 +4485,10 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>221</v>
+        <v>35</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>222</v>
+        <v>491</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>32</v>
@@ -3636,7 +4534,7 @@
         <v>35</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>205</v>
+        <v>492</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>32</v>
@@ -3659,7 +4557,7 @@
         <v>35</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>223</v>
+        <v>493</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>32</v>
@@ -3705,7 +4603,7 @@
         <v>35</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>206</v>
+        <v>494</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>32</v>
@@ -3728,7 +4626,7 @@
         <v>35</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>224</v>
+        <v>495</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>32</v>
@@ -3774,7 +4672,7 @@
         <v>35</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>207</v>
+        <v>496</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>32</v>
@@ -3800,7 +4698,7 @@
         <v>35</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>208</v>
+        <v>497</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>32</v>
@@ -3826,7 +4724,7 @@
         <v>35</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>209</v>
+        <v>498</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>32</v>
@@ -3862,12 +4760,12 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="22.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="26.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="22.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="26.265625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -3984,14 +4882,14 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="23.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.53125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="23.46484375" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -4025,7 +4923,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>211</v>
+        <v>508</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -4048,7 +4946,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>212</v>
+        <v>509</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -4071,7 +4969,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>213</v>
+        <v>510</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -4094,7 +4992,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>214</v>
+        <v>511</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -4117,7 +5015,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>215</v>
+        <v>512</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -4140,7 +5038,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>225</v>
+        <v>513</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -4160,7 +5058,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>226</v>
+        <v>514</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -4180,7 +5078,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>227</v>
+        <v>515</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -4205,14 +5103,14 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="14.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
+    <col min="8" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -4243,7 +5141,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>216</v>
+        <v>521</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -4266,7 +5164,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>217</v>
+        <v>522</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -4289,7 +5187,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>218</v>
+        <v>523</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -4312,7 +5210,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>219</v>
+        <v>524</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -4335,7 +5233,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>220</v>
+        <v>525</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -4363,12 +5261,12 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -4396,7 +5294,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>210</v>
+        <v>499</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
